--- a/AAII_Financials/Quarterly/TNL_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/TNL_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>TNL</t>
   </si>
@@ -656,416 +656,429 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="5.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E7" s="2">
         <v>46112</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>46022</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45930</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45838</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45747</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45657</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45565</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45473</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45382</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45291</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45199</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45107</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>45016</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44926</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44834</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44742</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44651</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44561</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44469</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44377</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44286</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44196</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44104</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>44012</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43921</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43830</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43738</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43646</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>1063000</v>
+      </c>
+      <c r="E8" s="3">
         <v>961000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>1025000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>1044000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>1018000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>934000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>971000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>993000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>985000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>916000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>936000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>986000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>949000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>879000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>899000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>937000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>922000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>809000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>870000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>839000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>797000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>628000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>645000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>614000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>343000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>558000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>981000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>1105000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>1039000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>918000</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>486000</v>
+      </c>
+      <c r="E9" s="3">
         <v>452000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>454000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>474000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>478000</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>468000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>440000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>461000</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>463000</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>472000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>435000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>471000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>460000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>450000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>457000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>476000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>467000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>438000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>437000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>414000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>410000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>335000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>322000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>311000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>208000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>392000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>452000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>536000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>497000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>453000</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>544000</v>
+      </c>
+      <c r="E10" s="3">
         <v>476000</v>
-      </c>
-      <c r="E10" s="3">
-        <v>537000</v>
       </c>
       <c r="F10" s="3">
         <v>537000</v>
       </c>
       <c r="G10" s="3">
+        <v>537000</v>
+      </c>
+      <c r="H10" s="3">
         <v>506000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>432000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>496000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>497000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>489000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>411000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>470000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>486000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>462000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>404000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>442000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>461000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>455000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>371000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>433000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>425000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>387000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>293000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>323000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>303000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>135000</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>166000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>529000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>569000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>542000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>465000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1098,8 +1111,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1190,8 +1204,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1282,100 +1299,106 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3">
         <v>22000</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>238000</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>8000</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>1000</v>
       </c>
-      <c r="H14" s="3" t="s">
+      <c r="I14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>-4000</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>16000</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
+      <c r="M14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N14" s="3">
         <v>15000</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>2000</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>10000</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>2000</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>17000</v>
       </c>
-      <c r="R14" s="3">
-        <v>0</v>
-      </c>
       <c r="S14" s="3">
+        <v>0</v>
+      </c>
+      <c r="T14" s="3">
         <v>-1000</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>10000</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>-4000</v>
-      </c>
-      <c r="V14" s="3">
-        <v>1000</v>
       </c>
       <c r="W14" s="3">
         <v>1000</v>
       </c>
       <c r="X14" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y14" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="3">
         <v>21000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>22000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>101000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>35000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>-35000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>7000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>23000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>18000</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1386,31 +1409,31 @@
         <v>32000</v>
       </c>
       <c r="F15" s="3">
-        <v>31000</v>
+        <v>32000</v>
       </c>
       <c r="G15" s="3">
         <v>31000</v>
       </c>
       <c r="H15" s="3">
+        <v>31000</v>
+      </c>
+      <c r="I15" s="3">
         <v>30000</v>
-      </c>
-      <c r="I15" s="3">
-        <v>29000</v>
       </c>
       <c r="J15" s="3">
         <v>29000</v>
       </c>
       <c r="K15" s="3">
-        <v>28000</v>
+        <v>29000</v>
       </c>
       <c r="L15" s="3">
         <v>28000</v>
       </c>
       <c r="M15" s="3">
+        <v>28000</v>
+      </c>
+      <c r="N15" s="3">
         <v>29000</v>
-      </c>
-      <c r="N15" s="3">
-        <v>28000</v>
       </c>
       <c r="O15" s="3">
         <v>28000</v>
@@ -1422,16 +1445,16 @@
         <v>28000</v>
       </c>
       <c r="R15" s="3">
+        <v>28000</v>
+      </c>
+      <c r="S15" s="3">
         <v>30000</v>
       </c>
-      <c r="S15" s="3">
+      <c r="T15" s="3">
         <v>31000</v>
       </c>
-      <c r="T15" s="3">
+      <c r="U15" s="3">
         <v>30000</v>
-      </c>
-      <c r="U15" s="3">
-        <v>31000</v>
       </c>
       <c r="V15" s="3">
         <v>31000</v>
@@ -1443,13 +1466,13 @@
         <v>31000</v>
       </c>
       <c r="Y15" s="3">
-        <v>32000</v>
+        <v>31000</v>
       </c>
       <c r="Z15" s="3">
         <v>32000</v>
       </c>
       <c r="AA15" s="3">
-        <v>31000</v>
+        <v>32000</v>
       </c>
       <c r="AB15" s="3">
         <v>31000</v>
@@ -1461,13 +1484,16 @@
         <v>31000</v>
       </c>
       <c r="AE15" s="3">
+        <v>31000</v>
+      </c>
+      <c r="AF15" s="3">
         <v>28000</v>
       </c>
-      <c r="AF15" s="3">
+      <c r="AG15" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1497,192 +1523,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>853000</v>
+      </c>
+      <c r="E17" s="3">
         <v>780000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>806000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>822000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>811000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>778000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>762000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>788000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>796000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>766000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>730000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>777000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>756000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>739000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>737000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>748000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>737000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>692000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>675000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>653000</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>646000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>541000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>560000</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>550000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>457000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>699000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>721000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>891000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>841000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>778000</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>210000</v>
+      </c>
+      <c r="E18" s="3">
         <v>181000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>219000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>222000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>207000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>156000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>209000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>205000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>189000</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>150000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>206000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>209000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>193000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>140000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>162000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>189000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>185000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>117000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>195000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>186000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>151000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>87000</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>85000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>64000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-114000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-141000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>260000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>214000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>198000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>140000</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1715,19 +1748,20 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-2000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-3000</v>
       </c>
-      <c r="E20" s="3">
-        <v>0</v>
-      </c>
       <c r="F20" s="3">
-        <v>-1000</v>
+        <v>0</v>
       </c>
       <c r="G20" s="3">
         <v>-1000</v>
@@ -1736,46 +1770,46 @@
         <v>-1000</v>
       </c>
       <c r="I20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="J20" s="3">
         <v>-2000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-4000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2000</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>-2000</v>
       </c>
-      <c r="O20" s="3" t="s">
+      <c r="P20" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>9000</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>21000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-6000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>4000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>6000</v>
-      </c>
-      <c r="V20" s="3">
-        <v>1000</v>
       </c>
       <c r="W20" s="3">
         <v>1000</v>
@@ -1784,203 +1818,209 @@
         <v>1000</v>
       </c>
       <c r="Y20" s="3">
+        <v>1000</v>
+      </c>
+      <c r="Z20" s="3">
         <v>5000</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>7000</v>
       </c>
       <c r="AA20" s="3">
         <v>7000</v>
       </c>
       <c r="AB20" s="3">
+        <v>7000</v>
+      </c>
+      <c r="AC20" s="3">
         <v>4000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>6000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>7000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>4000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>13000</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>244000</v>
+      </c>
+      <c r="E21" s="3">
         <v>216000</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>251000</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>254000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>239000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>187000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>240000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>235000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>221000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>180000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>235000</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>239000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>221000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>170000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>199000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>240000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>210000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>151000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>232000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>217000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>184000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>119000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>122000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>103000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-76000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-106000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>297000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>252000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>230000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>184000</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E22" s="3">
         <v>56000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>57000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>60000</v>
-      </c>
-      <c r="G22" s="3">
-        <v>57000</v>
       </c>
       <c r="H22" s="3">
         <v>57000</v>
       </c>
       <c r="I22" s="3">
+        <v>57000</v>
+      </c>
+      <c r="J22" s="3">
         <v>60000</v>
-      </c>
-      <c r="J22" s="3">
-        <v>63000</v>
       </c>
       <c r="K22" s="3">
         <v>63000</v>
       </c>
       <c r="L22" s="3">
+        <v>63000</v>
+      </c>
+      <c r="M22" s="3">
         <v>64000</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>68000</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>64000</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>61000</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>58000</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>52000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>48000</v>
-      </c>
-      <c r="S22" s="3">
-        <v>47000</v>
       </c>
       <c r="T22" s="3">
         <v>47000</v>
       </c>
       <c r="U22" s="3">
+        <v>47000</v>
+      </c>
+      <c r="V22" s="3">
         <v>51000</v>
-      </c>
-      <c r="V22" s="3">
-        <v>47000</v>
       </c>
       <c r="W22" s="3">
         <v>47000</v>
       </c>
       <c r="X22" s="3">
+        <v>47000</v>
+      </c>
+      <c r="Y22" s="3">
         <v>53000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>54000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>52000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>46000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>41000</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>40000</v>
       </c>
       <c r="AD22" s="3">
         <v>40000</v>
@@ -1989,194 +2029,203 @@
         <v>40000</v>
       </c>
       <c r="AF22" s="3">
+        <v>40000</v>
+      </c>
+      <c r="AG22" s="3">
         <v>41000</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>155000</v>
+      </c>
+      <c r="E23" s="3">
         <v>108000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-73000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>158000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>152000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>101000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>157000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>130000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>133000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>92000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>127000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>148000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>125000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>85000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>119000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>162000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>132000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>74000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>150000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>140000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>105000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>35000</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>36000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>19000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-153000</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-178000</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>226000</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>181000</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>162000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>112000</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>46000</v>
+      </c>
+      <c r="E24" s="3">
         <v>29000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>-12000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>47000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>44000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>28000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>39000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>33000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>36000</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>26000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>-2000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>38000</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>36000</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>22000</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>29000</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>46000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>32000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>23000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>40000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>39000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>31000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>6000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>31000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-21000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>11000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-44000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>71000</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>46000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>44000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2267,192 +2316,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>109000</v>
+      </c>
+      <c r="E26" s="3">
         <v>79000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-61000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>111000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>108000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>73000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>118000</v>
-      </c>
-      <c r="J26" s="3">
-        <v>97000</v>
       </c>
       <c r="K26" s="3">
         <v>97000</v>
       </c>
       <c r="L26" s="3">
+        <v>97000</v>
+      </c>
+      <c r="M26" s="3">
         <v>66000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>129000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>110000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>89000</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>63000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>90000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>116000</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>100000</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>51000</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>110000</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>101000</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>74000</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>29000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>5000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>40000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-164000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-134000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>155000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>135000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>118000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>109000</v>
+      </c>
+      <c r="E27" s="3">
         <v>79000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-61000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>111000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>108000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>73000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>119000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>97000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>129000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>66000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>129000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>110000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>94000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>64000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>90000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>116000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>100000</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>51000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>110000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>101000</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>74000</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>29000</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>5000</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>40000</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-164000</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-134000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>155000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>135000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>118000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>81000</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2543,8 +2601,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2564,17 +2625,17 @@
         <v>0</v>
       </c>
       <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
         <v>1000</v>
       </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
       <c r="K29" s="3">
+        <v>0</v>
+      </c>
+      <c r="L29" s="3">
         <v>32000</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
       <c r="M29" s="3">
         <v>0</v>
       </c>
@@ -2582,41 +2643,41 @@
         <v>0</v>
       </c>
       <c r="O29" s="3">
+        <v>0</v>
+      </c>
+      <c r="P29" s="3">
         <v>5000</v>
-      </c>
-      <c r="P29" s="3">
-        <v>1000</v>
       </c>
       <c r="Q29" s="3">
         <v>1000</v>
       </c>
       <c r="R29" s="3">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
+      <c r="T29" s="3">
+        <v>0</v>
+      </c>
+      <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
+      <c r="V29" s="3">
         <v>-3000</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
       <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
         <v>-2000</v>
       </c>
-      <c r="X29" s="3" t="s">
+      <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Z29" s="3">
         <v>-2000</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
       <c r="AA29" s="3">
         <v>0</v>
       </c>
@@ -2624,19 +2685,22 @@
         <v>0</v>
       </c>
       <c r="AC29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD29" s="3">
         <v>13000</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
       <c r="AE29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF29" s="3">
         <v>6000</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>-1000</v>
       </c>
     </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2727,8 +2791,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2819,19 +2886,22 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>2000</v>
+      </c>
+      <c r="E32" s="3">
         <v>3000</v>
       </c>
-      <c r="E32" s="3">
-        <v>0</v>
-      </c>
       <c r="F32" s="3">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="G32" s="3">
         <v>1000</v>
@@ -2840,46 +2910,46 @@
         <v>1000</v>
       </c>
       <c r="I32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="J32" s="3">
         <v>2000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>4000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2000</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>2000</v>
       </c>
-      <c r="O32" s="3" t="s">
+      <c r="P32" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-9000</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-21000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>6000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-4000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-6000</v>
-      </c>
-      <c r="V32" s="3">
-        <v>-1000</v>
       </c>
       <c r="W32" s="3">
         <v>-1000</v>
@@ -2888,123 +2958,129 @@
         <v>-1000</v>
       </c>
       <c r="Y32" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="Z32" s="3">
         <v>-5000</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>-7000</v>
       </c>
       <c r="AA32" s="3">
         <v>-7000</v>
       </c>
       <c r="AB32" s="3">
+        <v>-7000</v>
+      </c>
+      <c r="AC32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-6000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-7000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-13000</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>109000</v>
+      </c>
+      <c r="E33" s="3">
         <v>79000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-61000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>111000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>108000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>73000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>119000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>97000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>129000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>66000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>129000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>110000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>94000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>64000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>91000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>116000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>100000</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>51000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>107000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>101000</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>72000</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>29000</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3000</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>40000</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-164000</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-134000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>168000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>135000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>124000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>80000</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3095,197 +3171,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>109000</v>
+      </c>
+      <c r="E35" s="3">
         <v>79000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-61000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>111000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>108000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>73000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>119000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>97000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>129000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>66000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>129000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>110000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>94000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>64000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>91000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>116000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>100000</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>51000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>107000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>101000</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>72000</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>29000</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3000</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>40000</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-164000</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-134000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>168000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>135000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>124000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>80000</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E38" s="2">
         <v>46112</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>46022</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45930</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45838</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45747</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45657</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45565</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45473</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45382</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45291</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45199</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45107</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>45016</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44926</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44834</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44742</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44651</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44561</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44469</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44377</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44286</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44196</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44104</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>44012</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43921</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43830</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43738</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43646</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3318,8 +3403,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3352,100 +3438,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>282000</v>
+      </c>
+      <c r="E41" s="3">
         <v>254000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>253000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>240000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>212000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>188000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>167000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>194000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>166000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>479000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>282000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>238000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>214000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>196000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>550000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>169000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>241000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>381000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>369000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>346000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>328000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>322000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>1196000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>1276000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>1052000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>1018000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>355000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>250000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>257000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>217000</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3453,11 +3543,11 @@
         <v>0</v>
       </c>
       <c r="E42" s="3">
+        <v>0</v>
+      </c>
+      <c r="F42" s="3">
         <v>35000</v>
       </c>
-      <c r="F42" s="3">
-        <v>0</v>
-      </c>
       <c r="G42" s="3">
         <v>0</v>
       </c>
@@ -3465,11 +3555,11 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>34000</v>
       </c>
-      <c r="J42" s="3">
-        <v>0</v>
-      </c>
       <c r="K42" s="3">
         <v>0</v>
       </c>
@@ -3477,11 +3567,11 @@
         <v>0</v>
       </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>24000</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
         <v>0</v>
       </c>
@@ -3536,192 +3626,201 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2741000</v>
+      </c>
+      <c r="E43" s="3">
         <v>2761000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2922000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2765000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2743000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2751000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2900000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2764000</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2738000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2722000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2842000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2644000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2586000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2536000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2530000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2525000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2446000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>2407000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2440000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2417000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>2429000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>2464000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>2597000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>2643000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>2745000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>2929000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>3264000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>3255000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>3188000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>3157000</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>1179000</v>
+      </c>
+      <c r="E44" s="3">
         <v>1183000</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>1128000</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>1269000</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>1252000</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>1221000</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>1227000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>1208000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>1206000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>1187000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>1135000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1149000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1148000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1158000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1193000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1146000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1192000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1129000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1216000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1270000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1339000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1359000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1347000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1331000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1278000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1218000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1199000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1209000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1216000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1213000</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -3729,194 +3828,200 @@
         <v>7000</v>
       </c>
       <c r="E45" s="3">
+        <v>7000</v>
+      </c>
+      <c r="F45" s="3">
         <v>28000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>7000</v>
-      </c>
-      <c r="G45" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I45" s="3">
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3">
         <v>19000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>8000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>20000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>18000</v>
-      </c>
-      <c r="N45" s="3">
-        <v>19000</v>
       </c>
       <c r="O45" s="3">
         <v>19000</v>
       </c>
       <c r="P45" s="3">
+        <v>19000</v>
+      </c>
+      <c r="Q45" s="3">
         <v>22000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>340000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>342000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>348000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>394000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>355000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>324000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>322000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>348000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>325000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>324000</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>350000</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>374000</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>368000</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>346000</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>347000</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>361000</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>4655000</v>
+      </c>
+      <c r="E46" s="3">
         <v>4672000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>4753000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>4685000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>4626000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>4592000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>4723000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>4562000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>4535000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>4845000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>4706000</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>4451000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>4378000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>4303000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4613000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4182000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4227000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4311000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4380000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4357000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4418000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4493000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5465000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>5574000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>5425000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>5539000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>5186000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>5060000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>5008000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4948000</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E47" s="3">
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3">
         <v>18000</v>
-      </c>
-      <c r="F47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G47" s="3" t="s">
         <v>8</v>
@@ -3924,11 +4029,11 @@
       <c r="H47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I47" s="3">
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3">
         <v>18000</v>
-      </c>
-      <c r="J47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="K47" s="3" t="s">
         <v>8</v>
@@ -3936,11 +4041,11 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
+      <c r="M47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N47" s="3">
         <v>19000</v>
-      </c>
-      <c r="N47" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="O47" s="3" t="s">
         <v>8</v>
@@ -3948,8 +4053,8 @@
       <c r="P47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q47" s="3">
-        <v>0</v>
+      <c r="Q47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="R47" s="3">
         <v>0</v>
@@ -3996,192 +4101,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>606000</v>
+      </c>
+      <c r="E48" s="3">
         <v>608000</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>454000</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>683000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>644000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>638000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>482000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>645000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>643000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>658000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>554000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>705000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>718000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>728000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>720000</v>
-      </c>
-      <c r="R48" s="3">
-        <v>799000</v>
       </c>
       <c r="S48" s="3">
         <v>799000</v>
       </c>
       <c r="T48" s="3">
+        <v>799000</v>
+      </c>
+      <c r="U48" s="3">
         <v>816000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>768000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>760000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>731000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>745000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>758000</v>
-      </c>
-      <c r="Z48" s="3">
-        <v>783000</v>
       </c>
       <c r="AA48" s="3">
         <v>783000</v>
       </c>
       <c r="AB48" s="3">
+        <v>783000</v>
+      </c>
+      <c r="AC48" s="3">
         <v>819000</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>816000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>874000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>852000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>851000</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1169000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1171000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1335000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1175000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1180000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1177000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1331000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1186000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1184000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1190000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1308000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>1160000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>1165000</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>1168000</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>1162000</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>1161000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>1168000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>1177000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>1180000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>1184000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>1189000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>1191000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>1095000</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>1090000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>1096000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>1097000</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>1113000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>1108000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>1027000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>1031000</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4272,8 +4386,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4364,100 +4481,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>397000</v>
+      </c>
+      <c r="E52" s="3">
         <v>326000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>52000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>295000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>306000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>303000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>50000</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>251000</v>
-      </c>
-      <c r="K52" s="3">
-        <v>278000</v>
       </c>
       <c r="L52" s="3">
         <v>278000</v>
       </c>
       <c r="M52" s="3">
+        <v>278000</v>
+      </c>
+      <c r="N52" s="3">
         <v>19000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>288000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>293000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>232000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>262000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>238000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>283000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>296000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>260000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>300000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>301000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>299000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>295000</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>375000</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>293000</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>321000</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>338000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>521000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>579000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>540000</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4548,100 +4671,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>6896000</v>
+      </c>
+      <c r="E54" s="3">
         <v>6840000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>6760000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>6892000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>6809000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>6764000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>6735000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>6698000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>6693000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>7023000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>6738000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>6655000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>6602000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>6477000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>6757000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>6380000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>6477000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>6600000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>6588000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>6601000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>6639000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>6728000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>7613000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>7822000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>7597000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>7776000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>7453000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>7563000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>7466000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>7370000</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4674,8 +4803,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4708,145 +4838,149 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>59000</v>
+      </c>
+      <c r="E57" s="3">
         <v>63000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>62000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>66000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>69000</v>
-      </c>
-      <c r="H57" s="3">
-        <v>67000</v>
       </c>
       <c r="I57" s="3">
         <v>67000</v>
       </c>
       <c r="J57" s="3">
+        <v>67000</v>
+      </c>
+      <c r="K57" s="3">
         <v>55000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>50000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>65000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>73000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>71000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>70000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>61000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>65000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>66000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>70000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>67000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>62000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>60000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>56000</v>
-      </c>
-      <c r="X57" s="3">
-        <v>62000</v>
       </c>
       <c r="Y57" s="3">
         <v>62000</v>
       </c>
       <c r="Z57" s="3">
+        <v>62000</v>
+      </c>
+      <c r="AA57" s="3">
         <v>57000</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>61000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>71000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>73000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>86000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>81000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>79000</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>670000</v>
+      </c>
+      <c r="E58" s="3">
         <v>933000</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>936000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>908000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>604000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>580000</v>
       </c>
-      <c r="I58" s="3">
-        <v>0</v>
-      </c>
       <c r="J58" s="3">
+        <v>0</v>
+      </c>
+      <c r="K58" s="3">
         <v>520000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>599000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>565000</v>
       </c>
-      <c r="M58" s="3">
-        <v>0</v>
-      </c>
       <c r="N58" s="3">
+        <v>0</v>
+      </c>
+      <c r="O58" s="3">
         <v>525000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>537000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>256000</v>
       </c>
-      <c r="Q58" s="3">
-        <v>0</v>
-      </c>
       <c r="R58" s="3">
         <v>0</v>
       </c>
@@ -4892,8 +5026,11 @@
       <c r="AF58" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG58" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
@@ -4901,367 +5038,379 @@
         <v>1000</v>
       </c>
       <c r="E59" s="3">
+        <v>1000</v>
+      </c>
+      <c r="F59" s="3">
         <v>74000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1000</v>
-      </c>
-      <c r="G59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="H59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="I59" s="3">
+      <c r="I59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J59" s="3">
         <v>60000</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1000</v>
       </c>
-      <c r="K59" s="3" t="s">
+      <c r="L59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>65000</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1000</v>
-      </c>
-      <c r="O59" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="P59" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="Q59" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="R59" s="3">
         <v>1164000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1131000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1210000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1190000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1185000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1206000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>1243000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1210000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1219000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>1263000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>1328000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>1257000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>1334000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>1373000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>1321000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>1423000</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>1454000</v>
+      </c>
+      <c r="E60" s="3">
         <v>1596000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>1543000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>1596000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>1315000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>1138000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>572000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>1187000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>1225000</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>1187000</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>547000</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>1167000</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>1182000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>856000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1229000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1197000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1280000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1257000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1247000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1266000</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1299000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>1272000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1281000</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1320000</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>1389000</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>1328000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>1407000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>1459000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>1402000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>1502000</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>5201000</v>
+      </c>
+      <c r="E61" s="3">
         <v>4985000</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>4823000</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>4809000</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>5065000</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>5161000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>5670000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>5143000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>5062000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>5441000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>5733000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>5189000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>5133000</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>5304000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>5642000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>5273000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>5221000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>5328000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>5313000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>5343000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>5403000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>5569000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>6418000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>6641000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>6411000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>6394000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>5575000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>5541000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>5432000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>5291000</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>70000</v>
+      </c>
+      <c r="E62" s="3">
         <v>71000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>204000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>54000</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>53000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>78000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>194000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>21000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>68000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>97000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>246000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>96000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>94000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>103000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>790000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>813000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>822000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>826000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>822000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>841000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>855000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>863000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>882000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>854000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>847000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>945000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>995000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1133000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1192000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>1161000</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5352,8 +5501,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5444,8 +5596,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5536,100 +5691,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>7916000</v>
+      </c>
+      <c r="E66" s="3">
         <v>7863000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>7742000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>7713000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>7662000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>7667000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>7615000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>7559000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>7577000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>7948000</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>7655000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>7652000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>7606000</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>7452000</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>7670000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>7291000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>7331000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>7419000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>7389000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>7458000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>7564000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>7711000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>8588000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>8822000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>8653000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>8673000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>7983000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>8139000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>8031000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>7959000</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5662,8 +5823,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5754,8 +5916,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5846,8 +6011,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5938,8 +6106,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6030,100 +6201,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>2524000</v>
+      </c>
+      <c r="E72" s="3">
         <v>2453000</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>2412000</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>2510000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>2437000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>2367000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>2334000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>2250000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>2189000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>2097000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>2067000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>1971000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>1895000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>1836000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>1808000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>1750000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>1668000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>1603000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>1587000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>1511000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>1437000</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>1392000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>1390000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>1414000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>1399000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>1607000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>1785000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>1651000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>1558000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>1480000</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6214,8 +6391,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6306,8 +6486,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6398,100 +6581,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>-1019000</v>
+      </c>
+      <c r="E76" s="3">
         <v>-1022000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>-981000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>-821000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>-852000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>-903000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>-881000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>-862000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>-885000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>-926000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>-918000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>-1008000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>-1014000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>-984000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>-913000</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>-911000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>-854000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>-819000</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>-801000</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>-857000</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>-925000</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>-983000</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>-975000</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>-1000000</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>-1056000</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>-897000</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>-530000</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>-576000</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>-565000</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>-589000</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6582,197 +6771,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46203</v>
+      </c>
+      <c r="E80" s="2">
         <v>46112</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>46022</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45930</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45838</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45747</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45657</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45565</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45473</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45382</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45291</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45199</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45107</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>45016</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44926</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44834</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44742</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44651</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44561</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44469</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44377</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44286</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44196</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44104</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>44012</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43921</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43830</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43738</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43646</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43555</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>109000</v>
+      </c>
+      <c r="E81" s="3">
         <v>79000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-61000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>111000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>108000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>73000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>119000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>97000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>129000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>66000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>129000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>110000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>94000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>64000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>91000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>116000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>100000</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>51000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>107000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>101000</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>72000</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>29000</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3000</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>40000</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-164000</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-134000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>168000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>135000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>124000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>80000</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6805,82 +7003,83 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E83" s="3">
         <v>30000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>19000</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>30000</v>
       </c>
-      <c r="G83" s="3" t="s">
+      <c r="H83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>28000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>19000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>28000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>27000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>28000</v>
       </c>
-      <c r="M83" s="3" t="s">
+      <c r="N83" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>30000</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>31000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>30000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>28000</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>30000</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>31000</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>30000</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>31000</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>30000</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>32000</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>31000</v>
-      </c>
-      <c r="Y83" s="3">
-        <v>32000</v>
       </c>
       <c r="Z83" s="3">
         <v>32000</v>
       </c>
       <c r="AA83" s="3">
-        <v>31000</v>
+        <v>32000</v>
       </c>
       <c r="AB83" s="3">
         <v>31000</v>
@@ -6892,13 +7091,16 @@
         <v>31000</v>
       </c>
       <c r="AE83" s="3">
+        <v>31000</v>
+      </c>
+      <c r="AF83" s="3">
         <v>28000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>31000</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6989,8 +7191,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7081,8 +7286,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7173,8 +7381,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7265,8 +7476,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7357,100 +7571,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>220000</v>
+      </c>
+      <c r="E89" s="3">
         <v>38000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>124000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>163000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>232000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>121000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>98000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>145000</v>
       </c>
-      <c r="K89" s="3" t="s">
+      <c r="L89" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>47000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>152000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>88000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>103000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>7000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>175000</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>37000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>89000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>141000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>133000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>145000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>212000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>78000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>150000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>94000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>73000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>57000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>132000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>55000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>113000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>152000</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7483,100 +7703,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-25000</v>
+      </c>
+      <c r="E91" s="3">
         <v>-19000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-32000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-27000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-37000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-21000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-23000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-20000</v>
       </c>
-      <c r="K91" s="3" t="s">
+      <c r="L91" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-17000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-32000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-14000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-16000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-12000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-16000</v>
-      </c>
-      <c r="R91" s="3">
-        <v>-14000</v>
       </c>
       <c r="S91" s="3">
         <v>-14000</v>
       </c>
       <c r="T91" s="3">
+        <v>-14000</v>
+      </c>
+      <c r="U91" s="3">
         <v>-10000</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-17000</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-15000</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-13000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-12000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-13000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-17000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-18000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-21000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-33000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-25000</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-30000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-20000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7667,8 +7891,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7759,100 +7986,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-26000</v>
+      </c>
+      <c r="E94" s="3">
         <v>-18000</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-29000</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-30000</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-26000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-22000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-23000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-20000</v>
       </c>
-      <c r="K94" s="3" t="s">
+      <c r="L94" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-57000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-34000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-13000</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-16000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-17000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-16000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-13000</v>
-      </c>
-      <c r="T94" s="3">
-        <v>-16000</v>
       </c>
       <c r="U94" s="3">
         <v>-16000</v>
       </c>
       <c r="V94" s="3">
-        <v>-15000</v>
+        <v>-16000</v>
       </c>
       <c r="W94" s="3">
         <v>-15000</v>
       </c>
       <c r="X94" s="3">
+        <v>-15000</v>
+      </c>
+      <c r="Y94" s="3">
         <v>-47000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>33000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-62000</v>
-      </c>
-      <c r="AA94" s="3">
-        <v>-18000</v>
       </c>
       <c r="AB94" s="3">
         <v>-18000</v>
       </c>
       <c r="AC94" s="3">
+        <v>-18000</v>
+      </c>
+      <c r="AD94" s="3">
         <v>71000</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-70000</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-25000</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-42000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7885,73 +8118,74 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E96" s="3">
         <v>41000</v>
       </c>
-      <c r="E96" s="3">
+      <c r="F96" s="3">
         <v>35000</v>
       </c>
-      <c r="F96" s="3">
+      <c r="G96" s="3">
         <v>36000</v>
       </c>
-      <c r="G96" s="3">
+      <c r="H96" s="3">
         <v>37000</v>
       </c>
-      <c r="H96" s="3">
+      <c r="I96" s="3">
         <v>41000</v>
       </c>
-      <c r="I96" s="3">
+      <c r="J96" s="3">
         <v>34000</v>
       </c>
-      <c r="J96" s="3">
+      <c r="K96" s="3">
         <v>35000</v>
       </c>
-      <c r="K96" s="3" t="s">
+      <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>38000</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>32000</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>33000</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>34000</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>37000</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-32000</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-33000</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-35000</v>
       </c>
       <c r="T96" s="3">
         <v>-35000</v>
       </c>
       <c r="U96" s="3">
+        <v>-35000</v>
+      </c>
+      <c r="V96" s="3">
         <v>-30000</v>
       </c>
-      <c r="V96" s="3">
+      <c r="W96" s="3">
         <v>-26000</v>
       </c>
-      <c r="W96" s="3">
+      <c r="X96" s="3">
         <v>-27000</v>
-      </c>
-      <c r="X96" s="3">
-        <v>-26000</v>
       </c>
       <c r="Y96" s="3">
         <v>-26000</v>
@@ -7960,25 +8194,28 @@
         <v>-26000</v>
       </c>
       <c r="AA96" s="3">
-        <v>-43000</v>
+        <v>-26000</v>
       </c>
       <c r="AB96" s="3">
         <v>-43000</v>
       </c>
       <c r="AC96" s="3">
-        <v>-41000</v>
+        <v>-43000</v>
       </c>
       <c r="AD96" s="3">
         <v>-41000</v>
       </c>
       <c r="AE96" s="3">
-        <v>-42000</v>
+        <v>-41000</v>
       </c>
       <c r="AF96" s="3">
         <v>-42000</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>-42000</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8069,8 +8306,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8161,8 +8401,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8253,280 +8496,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-179000</v>
+      </c>
+      <c r="E100" s="3">
         <v>7000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-83000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-105000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-192000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-63000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-84000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-113000</v>
       </c>
-      <c r="K100" s="3" t="s">
+      <c r="L100" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>203000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-56000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-58000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-43000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-343000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>218000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-99000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-236000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-79000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-93000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-97000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-214000</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-884000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-273000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>177000</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-48000</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>646000</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-133000</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-35000</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-53000</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-68000</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>6000</v>
+      </c>
+      <c r="E101" s="3">
         <v>2000</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-11000</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>5000</v>
       </c>
-      <c r="G101" s="3" t="s">
+      <c r="H101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-4000</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>4000</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-3000</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
-      </c>
       <c r="L101" s="3">
+        <v>0</v>
+      </c>
+      <c r="M101" s="3">
         <v>-1000</v>
       </c>
-      <c r="M101" s="3" t="s">
+      <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-6000</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-9000</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>4000</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>6000</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-6000</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-9000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>4000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-1000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-5000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>2000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>9000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>3000</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>8000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-16000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>5000</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-6000</v>
-      </c>
-      <c r="AE101" s="3">
-        <v>1000</v>
       </c>
       <c r="AF101" s="3">
         <v>1000</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E102" s="3">
         <v>30000</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>12000</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>27000</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>20000</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>38000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-20000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>17000</v>
       </c>
-      <c r="K102" s="3">
-        <v>0</v>
-      </c>
       <c r="L102" s="3">
+        <v>0</v>
+      </c>
+      <c r="M102" s="3">
         <v>189000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>66000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>14000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>44000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-354000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>383000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-73000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-169000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>50000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>23000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>28000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-15000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-856000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-81000</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>212000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>15000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>669000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>75000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-56000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>36000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>43000</v>
       </c>
     </row>
